--- a/projection_library_kernel_v1.1/projection_library/sample_data/tier1_minimal_balance.xlsx
+++ b/projection_library_kernel_v1.1/projection_library/sample_data/tier1_minimal_balance.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -673,21 +673,6 @@
         <v>-1015</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Utile di esercizio</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>SP_equity</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>-265</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
